--- a/diseases/d236/2015-2019.xlsx
+++ b/diseases/d236/2015-2019.xlsx
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -21801,7 +21801,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24159,7 +24159,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24945,7 +24945,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25731,7 +25731,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -27159,7 +27159,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29517,7 +29517,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -31089,7 +31089,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32661,7 +32661,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33447,7 +33447,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34233,7 +34233,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -35019,7 +35019,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35805,7 +35805,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -37233,7 +37233,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -38019,7 +38019,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -38805,7 +38805,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -39591,7 +39591,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -41163,7 +41163,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -41949,7 +41949,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -42735,7 +42735,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -43521,7 +43521,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -44307,7 +44307,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -45093,7 +45093,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -45879,7 +45879,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN230" t="b">

--- a/diseases/d236/2015-2019.xlsx
+++ b/diseases/d236/2015-2019.xlsx
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -21801,7 +21801,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24159,7 +24159,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24945,7 +24945,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25731,7 +25731,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -27159,7 +27159,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29517,7 +29517,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -31089,7 +31089,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32661,7 +32661,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33447,7 +33447,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34233,7 +34233,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -35019,7 +35019,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35805,7 +35805,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -37233,7 +37233,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -38019,7 +38019,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -38805,7 +38805,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -39591,7 +39591,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -41163,7 +41163,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -41949,7 +41949,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -42735,7 +42735,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -43521,7 +43521,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -44307,7 +44307,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -45093,7 +45093,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -45879,7 +45879,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN230" t="b">
